--- a/out/Attention-MambaAMT_repeat_4_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.414642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.443095189965484</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002536328596372623</v>
+        <v>-0.0004015327648546081</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.924012279900067</v>
+        <v>4.629079677242723</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.852544555092029</v>
+        <v>9.265315227817705</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4384686620433414</v>
+        <v>0.694151169578656</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.801545218025808</v>
+        <v>6.018324876557495</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.548228552771</v>
+        <v>0.86791482415725</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.459603248032323</v>
+        <v>7.060113591339995</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7858828678023103</v>
+        <v>1.244151784428717</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.014642784948225</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.483450146107395</v>
+        <v>8.680992138790069</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8407393490988243</v>
+        <v>1.330995619960806</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.379104245191125</v>
+        <v>10.09892505265612</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8910135134338163</v>
+        <v>1.410587820312774</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.320457018309227</v>
+        <v>11.58920509367857</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.402098492715796</v>
+        <v>0.6365713822394468</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.23289858489791</v>
+        <v>11.45058917770579</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1941951934503571</v>
+        <v>0.3074355253079487</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.218875178920382</v>
+        <v>11.42838835436559</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09252761522460232</v>
+        <v>0.1464832619754544</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.209582224734404</v>
+        <v>11.41367643330077</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02741528696766202</v>
+        <v>0.04340233192742231</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.171786123898121</v>
+        <v>11.35384057573282</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01813418999885989</v>
+        <v>0.0287085435968385</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.180625137201415</v>
+        <v>11.36783363054517</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.009279600488117041</v>
+        <v>0.01469332154424463</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.18103787522832</v>
+        <v>11.36848994578955</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00474443196453744</v>
+        <v>0.007513759504690578</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.181241615529254</v>
+        <v>11.36881539964874</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001780491519634665</v>
+        <v>0.002821208280761271</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.180054568402596</v>
+        <v>11.36693911779061</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0009676820471878922</v>
+        <v>0.001535286159541811</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.18020927183935</v>
+        <v>11.36718697563016</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004638906708294137</v>
+        <v>0.0007372777738214787</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.180167930556808</v>
+        <v>11.36712444553203</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002852667596433369</v>
+        <v>0.0004545070398421638</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.180274354147118</v>
+        <v>11.3672958347411</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001463172661503614</v>
+        <v>0.0002348430136941102</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.18028258326786</v>
+        <v>11.36731177674677</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.893289167810316e-05</v>
+        <v>0.0001118938963018658</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.18027300703944</v>
+        <v>11.36729954135859</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.232841597722033e-05</v>
+        <v>6.919048991023728e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.180288698432528</v>
+        <v>11.36732725690503</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.598100299746031e-05</v>
+        <v>2.880272705146384e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.180279467095509</v>
+        <v>11.36731550921687</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>1.044053736228177e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.180271864112707</v>
+        <v>11.36730639825521</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>2.788397616378431e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.180267690941115</v>
+        <v>11.36730263917409</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-1.124731583660385e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.180261968662084</v>
+        <v>11.36729648258384</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.180256899306715</v>
+        <v>11.36729138934171</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.180252534332746</v>
+        <v>11.36728702436774</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.180253625579203</v>
+        <v>11.36728811561419</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.180252935972067</v>
+        <v>11.36728742600706</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.18025296628447</v>
+        <v>11.36728745631946</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.180252776831959</v>
+        <v>11.36728726686695</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.180252829878663</v>
+        <v>11.36728731991365</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.180252882925365</v>
+        <v>11.36728737296035</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.180252845034863</v>
+        <v>11.36728733506985</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.180252716207156</v>
+        <v>11.36728720624215</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.180252572223249</v>
+        <v>11.36728706225824</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.18025241308314</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.180252466129843</v>
+        <v>11.36728695616483</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.18025241308314</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.18025241308314</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.180252231208732</v>
+        <v>11.36728672124372</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.18025239792694</v>
+        <v>11.36728688796193</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.18025259495755</v>
+        <v>11.36728708499254</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.180252435817442</v>
+        <v>11.36728692585243</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.180252473707943</v>
+        <v>11.36728696374293</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.180252670738554</v>
+        <v>11.36728716077354</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.180252648004252</v>
+        <v>11.36728713803924</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.180252496442244</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.180252420661241</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.180252519176546</v>
+        <v>11.36728700921153</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.180252526754646</v>
+        <v>11.36728701678964</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.180252791988161</v>
+        <v>11.36728728202315</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.180252496442244</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.180252738941457</v>
+        <v>11.36728722897645</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.180252822300561</v>
+        <v>11.36728731233555</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.180252655582353</v>
+        <v>11.36728714561734</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.180252845034863</v>
+        <v>11.36728733506985</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.180252496442244</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.180252291833534</v>
+        <v>11.36728678186852</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.18025240550504</v>
+        <v>11.36728689554003</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.180252420661241</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.180252185740129</v>
+        <v>11.36728667577512</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.180252246364931</v>
+        <v>11.36728673639992</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.180252117537225</v>
+        <v>11.36728660757221</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.180252253943032</v>
+        <v>11.36728674397802</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.180252428239341</v>
+        <v>11.36728691827433</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.180252572223249</v>
+        <v>11.36728706225824</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.18025240550504</v>
+        <v>11.36728689554003</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.18025239792694</v>
+        <v>11.36728688796193</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.180252109959125</v>
+        <v>11.36728659999411</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.180252125115326</v>
+        <v>11.36728661515031</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.180252352458337</v>
+        <v>11.36728684249333</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.180252337302136</v>
+        <v>11.36728682733713</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.180252443395542</v>
+        <v>11.36728693343053</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.180252170583928</v>
+        <v>11.36728666061892</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.180252269099233</v>
+        <v>11.36728675913422</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.180252420661241</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.180252435817442</v>
+        <v>11.36728692585243</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.18025241308314</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.180252496442244</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.18025259495755</v>
+        <v>11.36728708499254</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.180252428239341</v>
+        <v>11.36728691827433</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.18025241308314</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.180252382770739</v>
+        <v>11.36728687280573</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.180252367614538</v>
+        <v>11.36728685764953</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.18025240550504</v>
+        <v>11.36728689554003</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.180252420661241</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.18025241308314</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823046</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823046</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.6238367016906172</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.6238367016906172</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002536328596372623</v>
+        <v>-0.0002018621619902551</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.924012279900067</v>
+        <v>2.327172596448186</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.852544555092029</v>
+        <v>4.65794258174856</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4384686620433414</v>
+        <v>0.3489699118321803</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.801545218025808</v>
+        <v>3.025586423237728</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.548228552771</v>
+        <v>0.4363258805156935</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.459603248032323</v>
+        <v>3.549323804869016</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7858828678023103</v>
+        <v>0.6254710804866676</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.483450146107395</v>
+        <v>4.364186535519984</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8407393490988243</v>
+        <v>0.6691305110034385</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.379104245191125</v>
+        <v>5.077022785714068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8910135134338163</v>
+        <v>0.7091427344160302</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.414642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.320457018309227</v>
+        <v>5.826229853252978</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.402098492715796</v>
+        <v>0.3200229268560261</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.414642784948225</v>
+        <v>0.482557801127078</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.23289858489791</v>
+        <v>5.756543533770214</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1941951934503571</v>
+        <v>0.1545570896928125</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.482557801127078</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.218875178920382</v>
+        <v>5.745382511826479</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09252761522460232</v>
+        <v>0.07364185178115142</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.209582224734404</v>
+        <v>5.737986385939209</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02741528696766202</v>
+        <v>0.02181920380304784</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.482557801127078</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.171786123898121</v>
+        <v>5.707905226220288</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01813418999885989</v>
+        <v>0.01443198517499831</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.180625137201415</v>
+        <v>5.714939439476756</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.009279600488117041</v>
+        <v>0.007384502931937154</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.18103787522832</v>
+        <v>5.715266912196348</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00474443196453744</v>
+        <v>0.003775016326163223</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.181241615529254</v>
+        <v>5.715428046115382</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001780491519634665</v>
+        <v>0.001415672989552465</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.180054568402596</v>
+        <v>5.714482269350177</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0009676820471878922</v>
+        <v>0.0007696806126458277</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.18020927183935</v>
+        <v>5.714604408862124</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004638906708294137</v>
+        <v>0.000367728346811856</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.180167930556808</v>
+        <v>5.714570490309872</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002852667596433369</v>
+        <v>0.0002262294525972344</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.180274354147118</v>
+        <v>5.714654251475033</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001463172661503614</v>
+        <v>0.0001154361914257978</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.18028258326786</v>
+        <v>5.714659790054523</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.893289167810316e-05</v>
+        <v>5.394649471632548e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.18027300703944</v>
+        <v>5.714651141439973</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.232841597722033e-05</v>
+        <v>3.209524495511864e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.180288698432528</v>
+        <v>5.714662639408053</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.598100299746031e-05</v>
+        <v>1.248416916455026e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.180279467095509</v>
+        <v>5.714654208020125</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>2.205584102398162e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823041</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.180271864112707</v>
+        <v>5.714647153165545</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.180267690941115</v>
+        <v>5.71464281462827</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.180261968662084</v>
+        <v>5.714637236333147</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.414642784948225</v>
+        <v>0.482557801127078</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.180256899306715</v>
+        <v>5.714632189712079</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.180252534332746</v>
+        <v>5.714632507992295</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.180253625579203</v>
+        <v>5.714633599238752</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.180252935972067</v>
+        <v>5.714632909631616</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.18025296628447</v>
+        <v>5.714632939944019</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.180252776831959</v>
+        <v>5.714632750491508</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.414642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.180252829878663</v>
+        <v>5.714632803538212</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.1706394502817697</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.180252882925365</v>
+        <v>5.714632856584914</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.180252845034863</v>
+        <v>5.714632818694412</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.180252716207156</v>
+        <v>5.714632689866705</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.180252572223249</v>
+        <v>5.714632545882798</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.18025241308314</v>
+        <v>5.714632386742689</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.180252466129843</v>
+        <v>5.714632439789392</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.18025241308314</v>
+        <v>5.714632386742689</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817697</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.18025241308314</v>
+        <v>5.714632386742689</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.180252231208732</v>
+        <v>5.71463220486828</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.18025239792694</v>
+        <v>5.714632371586489</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.18025259495755</v>
+        <v>5.714632568617099</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.180252435817442</v>
+        <v>5.714632409476991</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.180252473707943</v>
+        <v>5.714632447367492</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823035</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.180252670738554</v>
+        <v>5.714632644398103</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.180252648004252</v>
+        <v>5.714632621663801</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817697</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.180252496442244</v>
+        <v>5.714632470101793</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.414642784948225</v>
+        <v>0.482557801127078</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.180252420661241</v>
+        <v>5.714632394320789</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.180252519176546</v>
+        <v>5.714632492836095</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.180252526754646</v>
+        <v>5.714632500414195</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.180252791988161</v>
+        <v>5.71463276564771</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.180252496442244</v>
+        <v>5.714632470101793</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.180252738941457</v>
+        <v>5.714632712601006</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270781</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.180252822300561</v>
+        <v>5.71463279596011</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.180252655582353</v>
+        <v>5.714632629241902</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.180252845034863</v>
+        <v>5.714632818694412</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.180252496442244</v>
+        <v>5.714632470101793</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.180252291833534</v>
+        <v>5.714632265493083</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.18025240550504</v>
+        <v>5.714632379164589</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.180252420661241</v>
+        <v>5.714632394320789</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.180252185740129</v>
+        <v>5.714632159399678</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.180252246364931</v>
+        <v>5.71463222002448</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.180252117537225</v>
+        <v>5.714632091196774</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.180252253943032</v>
+        <v>5.714632227602581</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823052</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.180252428239341</v>
+        <v>5.71463240189889</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823052</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.180252572223249</v>
+        <v>5.714632545882798</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.18025240550504</v>
+        <v>5.714632379164589</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.18025239792694</v>
+        <v>5.714632371586489</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.180252109959125</v>
+        <v>5.714632083618674</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.180252125115326</v>
+        <v>5.714632098774874</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.180252352458337</v>
+        <v>5.714632326117886</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823054</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.180252337302136</v>
+        <v>5.714632310961685</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823054</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.180252443395542</v>
+        <v>5.714632417055091</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.180252170583928</v>
+        <v>5.714632144243477</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.414642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.180252269099233</v>
+        <v>5.714632242758782</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.180252420661241</v>
+        <v>5.714632394320789</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.180252435817442</v>
+        <v>5.714632409476991</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.18025241308314</v>
+        <v>5.714632386742689</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.180252496442244</v>
+        <v>5.714632470101793</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823052</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.18025259495755</v>
+        <v>5.714632568617099</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.180252428239341</v>
+        <v>5.71463240189889</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.18025241308314</v>
+        <v>5.714632386742689</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.4825578011270782</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.180252382770739</v>
+        <v>5.714632356430288</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.180252367614538</v>
+        <v>5.714632341274087</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.4825578011270782</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.18025240550504</v>
+        <v>5.714632379164589</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.180252420661241</v>
+        <v>5.714632394320789</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.1559591754226544</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.18025241308314</v>
+        <v>5.714632386742689</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01841203682124615</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.008649099618196487</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003059687092900276</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0103993434458971</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.008475977927446365</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.01178946625441313</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004661450162529945</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.01157043222337961</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.006172040477395058</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.009137470275163651</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.009946210309863091</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.00188177265226841</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.007022790610790253</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.009974611923098564</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01612182706594467</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.005586782470345497</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.003565369173884392</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001476986333727837</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.002736974507570267</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001424182206392288</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.002453751862049103</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001957718282938004</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.02936054971823046</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008878808468580246</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.02936054971823046</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.009290091693401337</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6238367016906172</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.006252247840166092</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6238367016906172</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.008748633787035942</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002363309264183044</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01210553199052811</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01993970200419426</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.01323782093822956</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01683489046990871</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0114133432507515</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.007833151146769524</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.005485896021127701</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01554002426564693</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.05155801028013229</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.02037340961396694</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.03938475251197815</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002018621619902551</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.327172596448186</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01161235012114048</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.65794258174856</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3489699118321803</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02190329693257809</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.025586423237728</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4363258805156935</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02141763456165791</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.549323804869016</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6254710804866676</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.05356428027153015</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.364186535519984</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6691305110034385</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.05243916064500809</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.335755052535926</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.077022785714068</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7091427344160302</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.03820629417896271</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.335755052535926</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.826229853252978</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3200229268560261</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.02925434894859791</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.482557801127078</v>
+        <v>-0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.756543533770214</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1545570896928125</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.006547810509800911</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.482557801127078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.745382511826479</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07364185178115142</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.005423111841082573</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.737986385939209</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02181920380304784</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003290506079792976</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.482557801127078</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.707905226220288</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01443198517499831</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01366879232227802</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.714939439476756</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007384502931937154</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.03226541727781296</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.715266912196348</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003775016326163223</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.007977442815899849</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.715428046115382</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001415672989552465</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.008792387321591377</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.714482269350177</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007696806126458277</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.00777205266058445</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.714604408862124</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000367728346811856</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.003638451918959618</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.714570490309872</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002262294525972344</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.001536661759018898</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6825578011270781</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.714654251475033</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001154361914257978</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.008027708157896996</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.714659790054523</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.394649471632548e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.05113893747329712</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.335755052535926</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.714651141439973</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.209524495511864e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.004139993339776993</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.714662639408053</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.02801324799656868</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6825578011270781</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.714654208020125</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.001514565199613571</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.02936054971823041</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.714647153165545</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01912951841950417</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.71464281462827</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01792066544294357</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.714637236333147</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.03922451287508011</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.482557801127078</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.714632189712079</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0614640861749649</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.335755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.714632507992295</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0360814556479454</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.335755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.714633599238752</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.00681726448237896</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.714632909631616</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001887070015072823</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.714632939944019</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01426544226706028</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6825578011270781</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.714632750491508</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.005606291815638542</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6825578011270781</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.714632803538212</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01494467817246914</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1706394502817697</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.714632856584914</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007883219048380852</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.714632818694412</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01078913174569607</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.714632689866705</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01694622822105885</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.714632545882798</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01107359118759632</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.714632386742689</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.009841663762927055</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.714632439789392</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.007059263065457344</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.714632386742689</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01042473316192627</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1706394502817697</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.714632386742689</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01465370692312717</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.71463220486828</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01599962078034878</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.714632371586489</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.03200429677963257</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.714632568617099</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0001525748521089554</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.714632409476991</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.02020295150578022</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.6825578011270781</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.714632447367492</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0001536067575216293</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.02936054971823035</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.714632644398103</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02271767146885395</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.714632621663801</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.008019858971238136</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1706394502817697</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.714632470101793</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.001831823959946632</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.482557801127078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.714632394320789</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001842739060521126</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.714632492836095</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01413397677242756</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.714632500414195</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01228704303503036</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.71463276564771</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.005238490179181099</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.714632470101793</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0111044030636549</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.714632712601006</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01343549508601427</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6825578011270781</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.71463279596011</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03285572677850723</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.714632629241902</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01818895898759365</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.714632818694412</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02333016321063042</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.714632470101793</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01002366840839386</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.714632265493083</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.001366576179862022</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.714632379164589</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02266011573374271</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.714632394320789</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01778602041304111</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.714632159399678</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01933924853801727</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.71463222002448</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01482668705284595</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.714632091196774</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02756803669035435</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.714632227602581</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.00470268540084362</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.02936054971823052</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.71463240189889</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01333130709826946</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.02936054971823052</v>
+        <v>0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.714632545882798</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.002749733626842499</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.714632379164589</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.03701983764767647</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.714632371586489</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01335903257131577</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.714632083618674</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.01212342269718647</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.714632098774874</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.005882816389203072</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6825578011270783</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.714632326117886</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.006176704540848732</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.02936054971823054</v>
+        <v>0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.714632310961685</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02277765609323978</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.02936054971823054</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.714632417055091</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004230298101902008</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1706394502817695</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.714632144243477</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.009648477658629417</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.714632242758782</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0006415471434593201</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.714632394320789</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001244163140654564</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.714632409476991</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.003469066694378853</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.714632386742689</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0009492300450801849</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.714632470101793</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.007079677656292915</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.02936054971823052</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.714632568617099</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.00745682418346405</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.71463240189889</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.002843365073204041</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.714632386742689</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005258649587631226</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4825578011270782</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.714632356430288</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.002834459766745567</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1706394502817695</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.714632341274087</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002038093283772469</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.714632379164589</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>1.547858119010925e-05</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1706394502817695</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.714632394320789</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.009409496560692787</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1559591754226544</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.714632386742689</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>
